--- a/data/content-review-batches/14_rows_131-140.xlsx
+++ b/data/content-review-batches/14_rows_131-140.xlsx
@@ -395,25 +395,16 @@
       </x:c>
       <x:c r="I2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">אופן הכנת הבצק:
-	1.	במיקסר עם וו גיטרה נערבב את החמאה ואבקת הסוכר לקרם אחיד.
-	2.	נוסיף את החלמונים ומחית הווניל ונערבב היטב.
-	3.	נכניס את הקורנפלור, הקמח, אבקת האפייה והמלח, ונערבב עד לקבלת בצק אחיד.
-	4.	נקרר את הבצק במקרר כ-20 דקות.
-	5.	נרדד את הבצק בין 2 ניירות אפייה ונחתוך לריבועים קטנים בגודל או נקרוץ עיגולים לעוגיות רגילות.
-	6.	נאפה בתנור שחומם מראש ל-170 מעלות טורבו למשך 8-10 דקות. העוגיות צריכות להישאר בהירות.
-הכנת שכבות הקינוח:
-	1.	נקציף את השמנת, הפודינג ואבקת הסוכר לקרם יציב.
-	2.	נחלק את הקרם לשניים:
-	•	חצי נשאיר כקרם וניל
-	•	לחצי השני נוסיף 2 כפות ריבת חלב ונקפל בעדינות עד לאיחוד
-	3.	נבנה את השכבות:
-	•	שכבת ריבועי עוגיות
-	•	קרם וניל
-	•	ריבת חלב
-	•	קוקוס טחון
-	•	קרם ריבת חלב
-הקינוח הכי טעים לאחר כמה שעות של התייצבות במקרר 
+          <x:t xml:space="preserve">אופן הכנת הבצק: 1.	במיקסר עם וו גיטרה נערבב את החמאה ואבקת הסוכר לקרם אחיד.
+2.	נוסיף את החלמונים ומחית הווניל ונערבב היטב.
+3.	נכניס את הקורנפלור, הקמח, אבקת האפייה והמלח, ונערבב עד לקבלת בצק אחיד.
+4.	נקרר את הבצק במקרר כ-20 דקות.
+5.	נרדד את הבצק בין 2 ניירות אפייה ונחתוך לריבועים קטנים בגודל או נקרוץ עיגולים לעוגיות רגילות.
+6.	נאפה בתנור שחומם מראש ל-170 מעלות טורבו למשך 8-10 דקות. העוגיות צריכות להישאר בהירות.
+הכנת שכבות הקינוח: 1.	נקציף את השמנת, הפודינג ואבקת הסוכר לקרם יציב.
+2.	נחלק את הקרם לשניים, חצי נשאיר כקרם וניל, לחצי השני נוסיף 2 כפות ריבת חלב ונקפל בעדינות עד לאיחוד
+3.	נבנה את השכבות, שכבת ריבועי עוגיות, קרם וניל, ריבת חלב, קוקוס טחון, קרם ריבת חלב
+הקינוח הכי טעים לאחר כמה שעות של התייצבות במקרר
 בתיאבון ❤️
 תייגו אותי אם הכנתם!
 *אם מכינים מהמתכון רק עוגיות אז יוצאות 70 עוגיות שזה 35 עוגיות אלפחורס</x:t>
@@ -754,20 +745,16 @@
       <x:c r="I6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">אופן ההכנה:
-לתחתית:
-מערבבים את הביסקוויטים הטחונים עם החמאה המומסת, שופכים לתבנית ומהדקים לתחתית ולדפנות
-גנאשים:
-בכל קערה ממיסים את השוקולד עם השמנת המתוקה בפולסים קצרים במיקרוגל עד שהתערובת חלקה מערבבים כל גנאש בנפרד ומניחים בצד להתקררות לטמפרטורת חדר 
+לתחתית: מערבבים את הביסקוויטים הטחונים עם החמאה המומסת, שופכים לתבנית ומהדקים לתחתית ולדפנות
+גנאשים: בכל קערה ממיסים את השוקולד עם השמנת המתוקה בפולסים קצרים במיקרוגל עד שהתערובת חלקה מערבבים כל גנאש בנפרד ומניחים בצד להתקררות לטמפרטורת חדר
 *חשוב לא לשלב את הגנאש עם הקרם כשהוא חם
-לקרם גבינה:
-בקערת מיקסר מקציפים את השמנת המתוקה עם הסוכר למשך כשתי דקות 
-מוסיפים את הגבינה הלבנה ואינסטנט הפודינג וממשיכים להקציף עד לקבלת קרם יציב וחלק מחלקים את הקרם ל־3 קערות שוות ומערבבים כל חלק עם אחד מהגנאשים הקרים עד שהצבע אחיד בכל קערה מעבירים כל קרם לשקית זילוף
-להרכבה:
-מזלפים את הקרמים בצורה אקראית למראה מנומר 
-כשנסיים לזלף את כל הקרמים היישר בעדינות את החלק העליון ונעביר למקרר 
-לגנאש הציפוי:
-ממיסים את השוקולד המריר והשוקולד חלב עם השמנת המתוקה בפולסים קצרים במיקרוגל או על בן מארי מערבבים עד שהגנאש חלק ואחיד מצננים מעט ויוצקים בעדינות מעל העוגה הקרה
-מעבירים את העוגה למקרר ללילה שלם או לפחות 6 שעות עד שהעוגה יציבה לגמרי 
+לקרם גבינה: בקערת מיקסר מקציפים את השמנת המתוקה עם הסוכר למשך כשתי דקות
+מוסיפים את הגבינה הלבנה ואינסטנט הפודינג וממשיכים להקציף עד לקבלת קרם יציב וחלק
+מחלקים את הקרם ל־3 קערות שוות ומערבבים כל חלק עם אחד מהגנאשים הקרים עד שהצבע אחיד בכל קערה מעבירים כל קרם לשקית זילוף
+להרכבה: מזלפים את הקרמים בצורה אקראית למראה מנומר
+כשנסיים לזלף את כל הקרמים היישר בעדינות את החלק העליון ונעביר למקרר
+לגנאש הציפוי: ממיסים את השוקולד המריר והשוקולד חלב עם השמנת המתוקה בפולסים קצרים במיקרוגל או על בן מארי מערבבים עד שהגנאש חלק ואחיד מצננים מעט ויוצקים בעדינות מעל העוגה הקרה
+מעבירים את העוגה למקרר ללילה שלם או לפחות 6 שעות עד שהעוגה יציבה לגמרי
 ובתאבון 🩷</x:t>
         </x:is>
       </x:c>
@@ -948,20 +935,16 @@
       <x:c r="I8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">אופן ההכנה
-בלילת כדורי שוקולד:
-מתחילים בהמסה של החמאה, החלב והשוקולד בלונדי בקלחת (אפשר גם במיקרו בפולסים של חצי דקה) עד שהתערובת חלקה. 
+בלילת כדורי שוקולד: מתחילים בהמסה של החמאה, החלב והשוקולד בלונדי בקלחת (אפשר גם במיקרו בפולסים של חצי דקה) עד שהתערובת חלקה.
 מוסיפים פנימה את הביסקוויטים הטחונים וקורט מלח, מערבבים היטב עד שנוצרת תערובת דביקה ואחידה. מקררים במקרר למשך שעה וחצי, עד שהבלילה מתייצבת ואפשר לרדד אותה.
-הכנת הקרם:
-בקערת מיקסר מקציפים את השמנת המתוקה יחד עם אבקת הסוכר במשך כשתי דקות. מוסיפים את אינסטנט הפודינג וממשיכים להקציף עוד כדקה-שתיים, עד שהקרם יציב במרקם חלק ואוורירי. שומרים בקירור עד להרכבה.
-הכנת הגנאש:
-שמים את השוקולד בלונדי והשמנת המתוקה בקערה, ממיסים במיקרו בפולסים של חצי דקה, עד שהכול נמס ואחיד. 
+הכנת הקרם: בקערת מיקסר מקציפים את השמנת המתוקה יחד עם אבקת הסוכר במשך כשתי דקות. מוסיפים את אינסטנט הפודינג וממשיכים להקציף עוד כדקה-שתיים, עד שהקרם יציב במרקם חלק ואוורירי. שומרים בקירור עד להרכבה.
+הכנת הגנאש: שמים את השוקולד בלונדי והשמנת המתוקה בקערה, ממיסים במיקרו בפולסים של חצי דקה, עד שהכול נמס ואחיד.
 מכניסים את הגנאש למקרר לרבע שעה, עד שהוא מתקרר ומסמיך מעט – כך שיהיה נעים לשפיכה על הרולדה בלי להמיס אותה.
-*מכינים את הגנאש רק אחרי שגלגלנו את העוגה והיא מתייצבת במקרר 
-הרכבה:
-כשהבלילה של הכדורי שוקולד יציבה, מניחים אותה בין שני ניירות אפייה ומרדדים לצורת מלבן. 
+*מכינים את הגנאש רק אחרי שגלגלנו את העוגה והיא מתייצבת במקרר
+הרכבה: כשהבלילה של הכדורי שוקולד יציבה, מניחים אותה בין שני ניירות אפייה ומרדדים לצורת מלבן.
 מורחים מעל את הקרם באופן אחיד, ומשאירים רווח בקצה כדי שהקרם לא יברח החוצה בזמן הגלגול. מגלגלים בעדינות לרולדה, כמו שמגלגלים עוגיות מגולגלות, ומכניסים למקרר להתייצבות בערך שעה
-כשהרולדה קרה ויציבה, מניחים אותה על רשת (עם נייר אפייה או תבנית מתחת) ויוצקים מעליה את הגנאש שהתקרר. 
-מכניסים את הרולדה ללילה במקרר או לפחות ל6 שעות 
+כשהרולדה קרה ויציבה, מניחים אותה על רשת (עם נייר אפייה או תבנית מתחת) ויוצקים מעליה את הגנאש שהתקרר.
+מכניסים את הרולדה ללילה במקרר או לפחות ל6 שעות
 ובתאבון 🩷🩷</x:t>
         </x:is>
       </x:c>
@@ -1137,36 +1120,30 @@
       </x:c>
       <x:c r="I10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">הכנת הקרם הבסיסי:
-מקציפים את השמנת המתוקה.
+          <x:t xml:space="preserve">הכנת הקרם הבסיסי: מקציפים את השמנת המתוקה.
 לאחר כשתי דקות מוסיפים את אינסטנט הפודינג ואבקת הסוכר.
 ממשיכים להקציף עד שמתקבלת קצפת יציבה.
 מחלקים את הקרם לשתי קערות שוות.
-קרם חמאת בוטנים:
-מוסיפים לקערה הראשונה 2 כפות חמאת בוטנים.
+קרם חמאת בוטנים: מוסיפים לקערה הראשונה 2 כפות חמאת בוטנים.
 מערבבים עד שהתערובת אחידה.
-קרם שוקולד חלב:
-ממיסים את השוקולד החלב עם 60 גרם שמנת מתוקה במיקרוגל עד שהתערובת חלקה.
+קרם שוקולד חלב: ממיסים את השוקולד החלב עם 60 גרם שמנת מתוקה במיקרוגל עד שהתערובת חלקה.
 מצננים מעט.
 מוסיפים לקערה השנייה של הקרם ומערבבים היטב.
 שימו לב לא לערבב את הגנאש עם הקרם כשהגנאש עדיין חם – חשוב שהגנאש יתקרר לגמרי לפני השילוב.
-הרכבת העוגה:
-טובלים את הביסקוויטים בחלב ומסדרים שכבה בתבנית.
+הרכבת העוגה: טובלים את הביסקוויטים בחלב ומסדרים שכבה בתבנית.
 מורחים מעל את קרם חמאת הבוטנים.
 מוסיפים שכבת ביסקוויטים נוספת.
 מורחים מעל את קרם השוקולד חלב.
 מכניסים את העוגה להתייצבות במקרר למשך שעה לפחות.
-הכנת הקרמל:
-ממיסים את הסוכר במחבת על אש בינונית, ללא ערבוב, עד שהוא נמס והופך לקרמל זהוב.
+הכנת הקרמל: ממיסים את הסוכר במחבת על אש בינונית, ללא ערבוב, עד שהוא נמס והופך לקרמל זהוב.
 מוסיפים בזהירות את השמנת החמה תוך ערבוב מתמיד.
 מוסיפים את החמאה ומערבבים עד שהיא נמסה לגמרי.
 מוסיפים קורט מלח והבוטנים הגרוסים.
 מערבבים היטב עד שהתערובת אחידה.
-ציפוי העוגה:
-כשהקרמל מתקרר לגמרי והעוגה קרה ומיוצבת, שופכים בעדינות את הקרמל מעליה ומיישרים.
+ציפוי העוגה: כשהקרמל מתקרר לגמרי והעוגה קרה ומיוצבת, שופכים בעדינות את הקרמל מעליה ומיישרים.
 מחזירים את העוגה למקרר עד להגשה.
-העוגה צריכה להתייצב לפחות לילה במקרר 
- בתאבון 🩷🩷</x:t>
+העוגה צריכה להתייצב לפחות לילה במקרר
+בתאבון 🩷🩷</x:t>
         </x:is>
       </x:c>
       <x:c r="J10" t="inlineStr">
@@ -1242,38 +1219,33 @@
 חמש עלי תימין
 בצק עלים
 ביצה טרופה
-שומשום</x:t>
+שומשום
+לרוטב טחינה ביתי:
+טחינה גולמית
+שני שיני שום
+קצת מיץ לימון טרי
+מלח
+פטרוזיליה טרייה
+מים קרים</x:t>
         </x:is>
       </x:c>
       <x:c r="I11" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">אופן הכנה
-תיבול הבשר:
-שמים את האסאדו בתבנית
+תיבול הבשר: שמים את האסאדו בתבנית
 שופכים מעל סילאן, חרדל, סויה, מלח, פלפל ופפריקה
 מערבבים ישירות בתבנית כדי שהרוטב יעטוף את כל הבשר
 מניחים מעל את שיני השום ועלי התימין
 עוטפים היטב את התבנית בנייר אפייה ואז בנייר כסף
 מכניסים לתנור שחומם ל-170 מעלות טורבו למשך ארבע שעות
 מוציאים ומפרקים את האסאדו לשערות דקות בעזרת הידיים
-הרכבת הבורקס:
-פותחים את בצק העלים למלבן
+הרכבת הבורקס: פותחים את בצק העלים למלבן
 מניחים במרכז שכבה נדיבה של אסאדו מפורק
 סוגרים את הבצק משני הצדדים ומהדקים
 מברישים בביצה ומפזרים שומשום
-אפייה:
-מכניסים לתנור שחומם ל-180 מעלות לחצי שעה עד שהבורקס זהוב ותפוח
+אפייה: מכניסים לתנור שחומם ל-180 מעלות לחצי שעה עד שהבורקס זהוב ותפוח
 (הזמן והחום עשויים להשתנות בהתאם לתנור)
-רוטב טחינה ביתי
-מצרכים:
-טחינה גולמית
-שני שיני שום
-קצת מיץ לימון טרי
-מלח
-פטרוזיליה טרייה
-מים קרים
-הכנה
-שמים את כל המרכיבים במעבד מזון ומעבדים עד לקבלת רוטב חלק וקרמי
+הכנה: שמים את כל המרכיבים במעבד מזון ומעבדים עד לקבלת רוטב חלק וקרמי
 מוסיפים מים לפי הצורך עד שמגיעים לסמיכות הרצויה
 בתאבון מחכה לשמוע איך יצא 🩷🩷</x:t>
         </x:is>
